--- a/data/trans_dic/P2B_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P2B_R-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas que requieren dedicación o cuidados especiales</t>
+          <t>Hogares con personas que requieren dedicación o cuidados especiales (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +639,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,69 +717,69 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>37,53; 59,53</t>
+          <t>37,15; 59,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>80,84; 98,06</t>
+          <t>80,26; 97,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49,99; 72,63</t>
+          <t>49,99; 73,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,92; 42,39</t>
+          <t>9,83; 43,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>30,17; 52,97</t>
+          <t>30,47; 52,46</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,56; 93,1</t>
+          <t>73,33; 93,08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,05; 84,7</t>
+          <t>66,56; 86,14</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,68; 16,02</t>
+          <t>4,56; 15,73</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>36,01; 52,29</t>
+          <t>36,86; 52,54</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>79,58; 93,38</t>
+          <t>79,51; 93,66</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>62,26; 77,27</t>
+          <t>62,45; 77,4</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,66; 24,75</t>
+          <t>8,45; 26,54</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,69 +857,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>22,2; 40,56</t>
+          <t>22,96; 40,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>63,71; 82,53</t>
+          <t>63,4; 82,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25,19; 43,31</t>
+          <t>25,2; 44,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,48; 21,32</t>
+          <t>6,47; 21,42</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,17; 29,81</t>
+          <t>13,92; 29,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>70,33; 87,56</t>
+          <t>69,59; 87,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,15; 49,21</t>
+          <t>30,85; 48,51</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15,37; 29,28</t>
+          <t>15,02; 29,02</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20,75; 33,58</t>
+          <t>20,1; 32,61</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>69,14; 82,89</t>
+          <t>69,62; 82,43</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29,5; 42,68</t>
+          <t>29,83; 43,07</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,08; 23,06</t>
+          <t>11,96; 22,99</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>20,53; 39,17</t>
+          <t>20,67; 39,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>68,94; 87,62</t>
+          <t>67,97; 87,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>33,84; 55,33</t>
+          <t>33,08; 54,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,24; 24,97</t>
+          <t>9,99; 25,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,43; 33,94</t>
+          <t>17,34; 33,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>64,21; 83,03</t>
+          <t>64,06; 82,79</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,05; 47,66</t>
+          <t>27,61; 47,87</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,22; 24,33</t>
+          <t>10,79; 23,89</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21,53; 34,1</t>
+          <t>21,27; 33,66</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>70,41; 83,0</t>
+          <t>69,89; 83,12</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>33,93; 48,82</t>
+          <t>33,74; 48,46</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12,49; 22,63</t>
+          <t>12,31; 22,15</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>22,37; 40,69</t>
+          <t>22,6; 40,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>92,2; 100,0</t>
+          <t>92,36; 100,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63,69; 84,65</t>
+          <t>63,61; 84,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25,16; 44,73</t>
+          <t>25,06; 44,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>21,3; 38,26</t>
+          <t>21,46; 39,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,51; 98,85</t>
+          <t>89,04; 98,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>68,64; 88,64</t>
+          <t>68,24; 88,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>37,86; 71,55</t>
+          <t>35,95; 70,36</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>24,33; 37,18</t>
+          <t>23,78; 36,87</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>93,31; 98,83</t>
+          <t>93,48; 98,84</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>70,36; 85,01</t>
+          <t>69,12; 83,63</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>34,26; 55,65</t>
+          <t>33,74; 55,92</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>13,17; 62,12</t>
+          <t>13,04; 62,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>63,22; 95,78</t>
+          <t>64,53; 95,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>92,0; 100,0</t>
+          <t>90,38; 100,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15,02; 37,3</t>
+          <t>15,3; 36,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,08; 56,58</t>
+          <t>11,83; 56,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>78,38; 97,39</t>
+          <t>77,76; 97,41</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>90,2; 100,0</t>
+          <t>91,26; 100,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>23,32; 47,94</t>
+          <t>21,62; 46,85</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>16,04; 51,55</t>
+          <t>16,63; 49,13</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>77,47; 95,05</t>
+          <t>76,56; 94,69</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>94,07; 100,0</t>
+          <t>93,54; 100,0</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>21,7; 37,63</t>
+          <t>21,83; 37,79</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1416,69 +1417,69 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12,79; 31,37</t>
+          <t>13,36; 32,64</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>60,05; 81,85</t>
+          <t>60,21; 81,9</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>46,02; 77,4</t>
+          <t>43,83; 75,41</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>22,48; 42,85</t>
+          <t>23,05; 43,31</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>19,14; 38,09</t>
+          <t>19,63; 39,04</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>68,4; 88,85</t>
+          <t>69,58; 88,63</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>61,85; 87,57</t>
+          <t>61,44; 87,74</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>31,0; 51,47</t>
+          <t>32,02; 52,89</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>18,64; 32,55</t>
+          <t>18,79; 32,0</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>68,34; 82,73</t>
+          <t>68,73; 83,49</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>59,72; 80,03</t>
+          <t>59,25; 79,51</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>29,87; 43,98</t>
+          <t>30,33; 45,17</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>18,1; 31,32</t>
+          <t>18,1; 31,53</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>68,33; 81,11</t>
+          <t>68,46; 81,61</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>52,47; 68,32</t>
+          <t>54,19; 68,61</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,5; 12,19</t>
+          <t>4,52; 12,42</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>23,31; 37,58</t>
+          <t>23,26; 37,26</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,27; 82,3</t>
+          <t>69,88; 82,3</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,84; 69,03</t>
+          <t>54,82; 69,12</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,09; 12,62</t>
+          <t>3,92; 12,73</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>22,42; 32,2</t>
+          <t>22,79; 32,56</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>71,7; 80,6</t>
+          <t>71,65; 80,81</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>56,07; 66,7</t>
+          <t>55,68; 66,18</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,99; 10,62</t>
+          <t>4,96; 10,86</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>31,36; 47,75</t>
+          <t>30,85; 47,39</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>85,63; 94,61</t>
+          <t>85,84; 94,49</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>91,44; 98,17</t>
+          <t>92,65; 98,1</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>73,51; 86,16</t>
+          <t>74,12; 86,67</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>29,19; 44,71</t>
+          <t>29,32; 45,26</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>84,12; 93,42</t>
+          <t>84,55; 93,56</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>88,48; 95,89</t>
+          <t>88,69; 96,03</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>75,23; 86,49</t>
+          <t>75,2; 86,52</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>32,46; 43,73</t>
+          <t>32,64; 43,64</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>86,38; 93,23</t>
+          <t>86,39; 92,94</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>91,51; 96,32</t>
+          <t>91,69; 96,22</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>76,65; 85,29</t>
+          <t>76,27; 84,71</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>28,18; 35,0</t>
+          <t>28,11; 35,02</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>79,61; 85,36</t>
+          <t>79,53; 85,39</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>64,57; 71,12</t>
+          <t>64,51; 71,45</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>26,45; 34,53</t>
+          <t>26,33; 34,56</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>27,03; 33,54</t>
+          <t>26,77; 33,47</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>81,08; 86,23</t>
+          <t>80,5; 85,83</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>66,34; 72,76</t>
+          <t>66,23; 72,9</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>31,04; 38,42</t>
+          <t>31,17; 38,36</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>28,41; 33,2</t>
+          <t>28,56; 33,24</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>81,2; 84,96</t>
+          <t>81,24; 84,98</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>66,74; 71,08</t>
+          <t>66,62; 71,17</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>30,1; 35,55</t>
+          <t>30,09; 35,55</t>
         </is>
       </c>
     </row>
@@ -1920,4 +1921,2040 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hogares con personas que requieren dedicación o cuidados especiales (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>23050</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>23454</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>27915</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>14546</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>20969</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>32238</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>39915</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>7372</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>44019</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>55694</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>67830</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>21918</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>17723; 28558</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>20351; 24843</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>22448; 32923</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>7201; 31991</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>15589; 26839</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>27924; 35446</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>34608; 44789</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>3616; 12483</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>36446; 51943</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>50439; 59418</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>60521; 75007</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>12904; 40512</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>20906</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>40173</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>23275</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>17866</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>13630</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>46832</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>29112</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>27062</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>34535</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>87005</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>52387</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>44928</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>15589; 27575</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>34483; 44788</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>17497; 31220</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>8132; 26920</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>9041; 19367</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>40978; 51308</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>23097; 36313</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>18950; 36614</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>26698; 43312</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>78864; 93369</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>43041; 62153</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>30128; 57897</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>19103</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>41838</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>24526</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>9599</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>16856</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>44798</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>24331</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>11359</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>35959</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>86637</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>48858</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>20958</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>13371; 25786</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>35829; 45956</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>18477; 30373</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>5764; 14509</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>11774; 22833</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>38394; 49621</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>17698; 30686</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>7248; 16044</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>28210; 44627</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>78729; 93627</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>40472; 58135</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>15363; 27652</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>20293</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>48450</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>33770</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>23789</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>21551</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>53514</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>37347</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>39939</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>41844</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>101964</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>71117</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>63728</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>14925; 26546</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>45884; 49680</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>28698; 38109</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>17579; 31233</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>15779; 28865</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>49391; 54838</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>32045; 41471</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>27885; 54572</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>33185; 51464</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>98292; 103927</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>63643; 76999</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>49836; 82589</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>3267</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>14974</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>31747</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>8552</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>3508</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>22634</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>34906</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>13601</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>6776</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>37608</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>66651</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>22153</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>1244; 5970</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>11643; 17320</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>29260; 32375</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>5281; 12628</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1348; 6434</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>19153; 23993</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>32412; 35516</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>8803; 19078</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>3482; 10288</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>32670; 40407</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>63504; 67890</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>16425; 28431</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>10092</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>32093</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>16462</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>14860</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>14749</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>39740</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>24279</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>23259</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>24840</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>71834</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>40742</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>38120</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>6232; 15230</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>26819; 36481</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>11632; 20013</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>10642; 19994</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>10260; 20406</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>34464; 43901</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>19265; 27511</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>17989; 29715</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>18594; 31659</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>64659; 78545</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>34301; 46030</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>31039; 46230</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>26951</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>87954</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>68882</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>9421</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>33284</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>93824</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>72582</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>11507</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>60235</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>181776</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>141464</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>20928</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>20030; 34883</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>79901; 95238</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>60777; 76942</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>5633; 15459</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>25773; 41284</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>85103; 100219</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>64533; 81368</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>6110; 19866</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>50474; 72090</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>170868; 192722</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>127986; 152138</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>13909; 30471</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>327</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>393</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>329</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>35433</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>104869</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>124370</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>106050</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>35492</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>116219</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>129200</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>127034</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>70925</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>221088</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>253569</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>233085</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>27820; 42728</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>99184; 109172</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>120127; 127191</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>97562; 114075</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>28315; 43713</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>109773; 121478</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>123477; 133690</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>117416; 135090</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>60951; 81492</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>211971; 228047</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>246524; 258722</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>219482; 243749</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>569</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>535</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>305</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>639</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>571</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>352</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>1208</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>1106</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>159096</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>393806</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>350945</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>204684</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>160038</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>449801</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>391673</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>261135</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>319134</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>843606</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>742618</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>465819</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>141510; 176257</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>379315; 407294</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>332904; 368716</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>174745; 229342</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>141508; 176911</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>433225; 461879</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>372009; 409489</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>236671; 291279</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>294665; 343019</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>824703; 862665</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>717982; 767086</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>428080; 505781</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/P2B_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P2B_R-Provincia-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>37,15; 59,86</t>
+          <t>35,85; 59,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>80,26; 97,97</t>
+          <t>79,53; 97,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49,99; 73,31</t>
+          <t>51,13; 74,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,83; 43,66</t>
+          <t>9,36; 38,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>30,47; 52,46</t>
+          <t>29,89; 52,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,33; 93,08</t>
+          <t>73,04; 93,59</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,56; 86,14</t>
+          <t>66,34; 85,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,56; 15,73</t>
+          <t>4,85; 15,51</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>36,86; 52,54</t>
+          <t>36,62; 52,54</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>79,51; 93,66</t>
+          <t>80,22; 94,14</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>62,45; 77,4</t>
+          <t>62,15; 76,94</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,45; 26,54</t>
+          <t>8,95; 26,43</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>22,96; 40,62</t>
+          <t>22,42; 40,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>63,4; 82,35</t>
+          <t>62,9; 82,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25,2; 44,96</t>
+          <t>25,49; 43,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,47; 21,42</t>
+          <t>7,0; 21,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,92; 29,83</t>
+          <t>13,92; 29,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>69,59; 87,13</t>
+          <t>69,55; 86,76</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,85; 48,51</t>
+          <t>29,42; 48,25</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15,02; 29,02</t>
+          <t>14,68; 30,01</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20,1; 32,61</t>
+          <t>20,78; 32,05</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>69,62; 82,43</t>
+          <t>70,18; 82,73</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29,83; 43,07</t>
+          <t>30,04; 43,27</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,96; 22,99</t>
+          <t>11,87; 23,5</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>20,67; 39,86</t>
+          <t>20,55; 39,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>67,97; 87,18</t>
+          <t>68,48; 87,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>33,08; 54,38</t>
+          <t>32,36; 55,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,99; 25,15</t>
+          <t>10,34; 25,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,34; 33,63</t>
+          <t>17,42; 33,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>64,06; 82,79</t>
+          <t>65,35; 83,13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27,61; 47,87</t>
+          <t>28,75; 48,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,79; 23,89</t>
+          <t>10,9; 25,53</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21,27; 33,66</t>
+          <t>21,5; 33,75</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>69,89; 83,12</t>
+          <t>70,3; 83,21</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>33,74; 48,46</t>
+          <t>33,96; 48,4</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12,31; 22,15</t>
+          <t>11,88; 22,35</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>22,6; 40,19</t>
+          <t>22,21; 40,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>92,36; 100,0</t>
+          <t>92,24; 100,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63,61; 84,47</t>
+          <t>62,72; 84,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25,06; 44,53</t>
+          <t>24,18; 45,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>21,46; 39,26</t>
+          <t>20,98; 38,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,04; 98,86</t>
+          <t>90,29; 98,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>68,24; 88,31</t>
+          <t>67,47; 88,34</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>35,95; 70,36</t>
+          <t>36,71; 69,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>23,78; 36,87</t>
+          <t>24,09; 36,56</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>93,48; 98,84</t>
+          <t>93,62; 98,85</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>69,12; 83,63</t>
+          <t>68,71; 84,03</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>33,74; 55,92</t>
+          <t>34,77; 56,57</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>13,04; 62,57</t>
+          <t>13,0; 62,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>64,53; 95,99</t>
+          <t>62,82; 95,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>90,38; 100,0</t>
+          <t>89,36; 100,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15,3; 36,59</t>
+          <t>15,48; 37,13</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,83; 56,44</t>
+          <t>12,1; 55,94</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>77,76; 97,41</t>
+          <t>79,12; 97,44</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>91,26; 100,0</t>
+          <t>91,19; 100,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>21,62; 46,85</t>
+          <t>21,97; 47,17</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>16,63; 49,13</t>
+          <t>16,31; 50,58</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>76,56; 94,69</t>
+          <t>76,91; 94,65</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>93,54; 100,0</t>
+          <t>92,73; 100,0</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>21,83; 37,79</t>
+          <t>21,28; 38,19</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13,36; 32,64</t>
+          <t>12,79; 32,02</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>60,21; 81,9</t>
+          <t>60,13; 82,53</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>43,83; 75,41</t>
+          <t>45,47; 75,5</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>23,05; 43,31</t>
+          <t>21,96; 42,61</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>19,63; 39,04</t>
+          <t>19,32; 39,11</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>69,58; 88,63</t>
+          <t>69,57; 88,28</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>61,44; 87,74</t>
+          <t>62,2; 87,88</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>32,02; 52,89</t>
+          <t>31,34; 51,03</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>18,79; 32,0</t>
+          <t>18,6; 32,6</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>68,73; 83,49</t>
+          <t>69,1; 83,2</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>59,25; 79,51</t>
+          <t>59,38; 80,0</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>30,33; 45,17</t>
+          <t>30,49; 44,8</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>18,1; 31,53</t>
+          <t>17,27; 31,11</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>68,46; 81,61</t>
+          <t>68,51; 81,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>54,19; 68,61</t>
+          <t>53,87; 68,7</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,52; 12,42</t>
+          <t>3,95; 11,91</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>23,26; 37,26</t>
+          <t>23,72; 37,46</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,88; 82,3</t>
+          <t>71,03; 83,19</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>54,82; 69,12</t>
+          <t>54,26; 68,24</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,92; 12,73</t>
+          <t>4,1; 12,33</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>22,79; 32,56</t>
+          <t>23,02; 32,39</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>71,65; 80,81</t>
+          <t>71,45; 80,27</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>55,68; 66,18</t>
+          <t>55,98; 66,21</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,96; 10,86</t>
+          <t>5,11; 10,85</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>30,85; 47,39</t>
+          <t>31,2; 48,16</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>85,84; 94,49</t>
+          <t>85,75; 94,58</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>92,65; 98,1</t>
+          <t>92,13; 98,09</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>74,12; 86,67</t>
+          <t>73,94; 86,6</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>29,32; 45,26</t>
+          <t>29,17; 44,33</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>84,55; 93,56</t>
+          <t>83,71; 93,07</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>88,69; 96,03</t>
+          <t>88,28; 95,67</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>75,2; 86,52</t>
+          <t>74,9; 86,59</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>32,64; 43,64</t>
+          <t>32,68; 44,05</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>86,39; 92,94</t>
+          <t>86,41; 92,87</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>91,69; 96,22</t>
+          <t>91,75; 96,38</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>76,27; 84,71</t>
+          <t>76,59; 85,06</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>28,11; 35,02</t>
+          <t>28,48; 34,87</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>79,53; 85,39</t>
+          <t>79,67; 85,52</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>64,51; 71,45</t>
+          <t>64,84; 71,83</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>26,33; 34,56</t>
+          <t>26,65; 34,43</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>26,77; 33,47</t>
+          <t>27,52; 34,08</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>80,5; 85,83</t>
+          <t>81,05; 86,03</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>66,23; 72,9</t>
+          <t>66,42; 72,96</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>31,17; 38,36</t>
+          <t>30,85; 38,18</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>28,56; 33,24</t>
+          <t>28,59; 33,27</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>81,24; 84,98</t>
+          <t>81,03; 84,86</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>66,62; 71,17</t>
+          <t>66,66; 71,2</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>30,09; 35,55</t>
+          <t>29,96; 35,62</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>17723; 28558</t>
+          <t>17104; 28231</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>20351; 24843</t>
+          <t>20165; 24842</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>22448; 32923</t>
+          <t>22963; 33397</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7201; 31991</t>
+          <t>6862; 28284</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>15589; 26839</t>
+          <t>15291; 26875</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27924; 35446</t>
+          <t>27814; 35639</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34608; 44789</t>
+          <t>34490; 44481</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3616; 12483</t>
+          <t>3848; 12313</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>36446; 51943</t>
+          <t>36211; 51951</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>50439; 59418</t>
+          <t>50890; 59722</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>60521; 75007</t>
+          <t>60226; 74554</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>12904; 40512</t>
+          <t>13654; 40342</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15589; 27575</t>
+          <t>15219; 27306</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>34483; 44788</t>
+          <t>34208; 44980</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17497; 31220</t>
+          <t>17697; 30188</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8132; 26920</t>
+          <t>8794; 26491</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9041; 19367</t>
+          <t>9042; 19323</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>40978; 51308</t>
+          <t>40955; 51088</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23097; 36313</t>
+          <t>22021; 36119</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18950; 36614</t>
+          <t>18518; 37861</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>26698; 43312</t>
+          <t>27605; 42571</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>78864; 93369</t>
+          <t>79498; 93708</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>43041; 62153</t>
+          <t>43348; 62433</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>30128; 57897</t>
+          <t>29880; 59166</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>13371; 25786</t>
+          <t>13294; 25574</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>35829; 45956</t>
+          <t>36100; 46298</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18477; 30373</t>
+          <t>18075; 31178</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5764; 14509</t>
+          <t>5965; 14583</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>11774; 22833</t>
+          <t>11831; 23051</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>38394; 49621</t>
+          <t>39168; 49823</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17698; 30686</t>
+          <t>18430; 31179</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7248; 16044</t>
+          <t>7320; 17145</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>28210; 44627</t>
+          <t>28506; 44758</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>78729; 93627</t>
+          <t>79190; 93729</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>40472; 58135</t>
+          <t>40743; 58059</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>15363; 27652</t>
+          <t>14834; 27906</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14925; 26546</t>
+          <t>14673; 26708</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>45884; 49680</t>
+          <t>45822; 49680</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>28698; 38109</t>
+          <t>28296; 37935</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17579; 31233</t>
+          <t>16960; 31976</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>15779; 28865</t>
+          <t>15423; 28006</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>49391; 54838</t>
+          <t>50088; 54840</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>32045; 41471</t>
+          <t>31684; 41486</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>27885; 54572</t>
+          <t>28474; 53982</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>33185; 51464</t>
+          <t>33619; 51031</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>98292; 103927</t>
+          <t>98446; 103946</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>63643; 76999</t>
+          <t>63259; 77366</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>49836; 82589</t>
+          <t>51360; 83557</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1244; 5970</t>
+          <t>1240; 5985</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>11643; 17320</t>
+          <t>11334; 17198</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>29260; 32375</t>
+          <t>28932; 32375</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5281; 12628</t>
+          <t>5342; 12814</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1348; 6434</t>
+          <t>1380; 6377</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>19153; 23993</t>
+          <t>19488; 23999</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>32412; 35516</t>
+          <t>32385; 35516</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>8803; 19078</t>
+          <t>8946; 19206</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3482; 10288</t>
+          <t>3415; 10592</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>32670; 40407</t>
+          <t>32820; 40390</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>63504; 67890</t>
+          <t>62953; 67890</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>16425; 28431</t>
+          <t>16008; 28728</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6232; 15230</t>
+          <t>5968; 14939</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>26819; 36481</t>
+          <t>26785; 36760</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11632; 20013</t>
+          <t>12066; 20036</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10642; 19994</t>
+          <t>10136; 19673</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>10260; 20406</t>
+          <t>10101; 20444</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>34464; 43901</t>
+          <t>34462; 43726</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19265; 27511</t>
+          <t>19504; 27557</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>17989; 29715</t>
+          <t>17611; 28671</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>18594; 31659</t>
+          <t>18402; 32249</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>64659; 78545</t>
+          <t>65005; 78271</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>34301; 46030</t>
+          <t>34376; 46312</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>31039; 46230</t>
+          <t>31213; 45854</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>20030; 34883</t>
+          <t>19108; 34423</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>79901; 95238</t>
+          <t>79954; 95179</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>60777; 76942</t>
+          <t>60412; 77042</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5633; 15459</t>
+          <t>4921; 14834</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>25773; 41284</t>
+          <t>26276; 41506</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>85103; 100219</t>
+          <t>86500; 101308</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>64533; 81368</t>
+          <t>63879; 80337</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>6110; 19866</t>
+          <t>6392; 19235</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>50474; 72090</t>
+          <t>50972; 71727</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>170868; 192722</t>
+          <t>170400; 191439</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>127986; 152138</t>
+          <t>128681; 152188</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>13909; 30471</t>
+          <t>14347; 30428</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>27820; 42728</t>
+          <t>28134; 43426</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>99184; 109172</t>
+          <t>99072; 109273</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>120127; 127191</t>
+          <t>119453; 127179</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>97562; 114075</t>
+          <t>97323; 113982</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>28315; 43713</t>
+          <t>28170; 42811</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>109773; 121478</t>
+          <t>108692; 120835</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>123477; 133690</t>
+          <t>122903; 133196</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>117416; 135090</t>
+          <t>116941; 135201</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>60951; 81492</t>
+          <t>61024; 82255</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>211971; 228047</t>
+          <t>212024; 227889</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>246524; 258722</t>
+          <t>246704; 259139</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>219482; 243749</t>
+          <t>220382; 244777</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>141510; 176257</t>
+          <t>143346; 175521</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>379315; 407294</t>
+          <t>380002; 407906</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>332904; 368716</t>
+          <t>334612; 370677</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>174745; 229342</t>
+          <t>176846; 228486</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>141508; 176911</t>
+          <t>145465; 180130</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>433225; 461879</t>
+          <t>436171; 462974</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>372009; 409489</t>
+          <t>373103; 409824</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>236671; 291279</t>
+          <t>234238; 289888</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>294665; 343019</t>
+          <t>295036; 343331</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>824703; 862665</t>
+          <t>822566; 861399</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>717982; 767086</t>
+          <t>718387; 767403</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>428080; 505781</t>
+          <t>426337; 506888</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2B_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P2B_R-Provincia-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>40,98%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>84,66%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>76,77%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>9,71%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>48,32%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>92,5%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>62,16%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>19,85%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>40,98%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>84,66%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>76,77%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>11,27%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>35,85; 59,18</t>
+          <t>30,17; 52,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>79,53; 97,97</t>
+          <t>73,56; 93,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>51,13; 74,37</t>
+          <t>66,05; 84,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,36; 38,6</t>
+          <t>4,89; 16,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>29,89; 52,53</t>
+          <t>37,53; 59,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,04; 93,59</t>
+          <t>80,84; 98,06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,34; 85,55</t>
+          <t>49,99; 72,63</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,85; 15,51</t>
+          <t>7,09; 21,99</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>36,62; 52,54</t>
+          <t>36,01; 52,29</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>80,22; 94,14</t>
+          <t>79,58; 93,38</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>62,15; 76,94</t>
+          <t>62,26; 77,27</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,95; 26,43</t>
+          <t>7,03; 16,05</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>20,99%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>79,53%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>38,89%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>20,84%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>30,79%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>73,87%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>33,52%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>14,22%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>20,99%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>79,53%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>38,89%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>19,3%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>22,42; 40,22</t>
+          <t>14,17; 29,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>62,9; 82,71</t>
+          <t>70,33; 87,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25,49; 43,48</t>
+          <t>30,15; 49,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,0; 21,08</t>
+          <t>14,4; 28,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,92; 29,76</t>
+          <t>22,2; 40,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>69,55; 86,76</t>
+          <t>63,71; 82,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,42; 48,25</t>
+          <t>25,19; 43,31</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,68; 30,01</t>
+          <t>11,62; 24,76</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20,78; 32,05</t>
+          <t>20,75; 33,58</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>70,18; 82,73</t>
+          <t>69,14; 82,89</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30,04; 43,27</t>
+          <t>29,5; 42,68</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,87; 23,5</t>
+          <t>15,12; 25,18</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>24,82%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>74,75%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>37,96%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>16,54%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>29,53%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>79,37%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>43,91%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>16,64%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>24,82%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>74,75%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>37,96%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,62%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>20,55; 39,53</t>
+          <t>17,43; 33,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>68,48; 87,83</t>
+          <t>64,21; 83,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32,36; 55,82</t>
+          <t>28,05; 47,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,34; 25,28</t>
+          <t>10,05; 23,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,42; 33,95</t>
+          <t>20,53; 39,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>65,35; 83,13</t>
+          <t>68,94; 87,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,75; 48,64</t>
+          <t>33,84; 55,33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,9; 25,53</t>
+          <t>10,2; 25,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21,5; 33,75</t>
+          <t>21,53; 34,1</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>70,3; 83,21</t>
+          <t>70,41; 83,0</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>33,96; 48,4</t>
+          <t>33,93; 48,82</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,88; 22,35</t>
+          <t>12,34; 22,33</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>29,31%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>96,47%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>79,53%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>50,65%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>30,72%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>97,52%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>74,86%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>33,91%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>29,31%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>96,47%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>79,53%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>42,24%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>22,21; 40,43</t>
+          <t>21,3; 38,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>92,24; 100,0</t>
+          <t>90,51; 98,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>62,72; 84,09</t>
+          <t>68,64; 88,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24,18; 45,59</t>
+          <t>36,9; 69,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>20,98; 38,09</t>
+          <t>22,37; 40,69</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,29; 98,86</t>
+          <t>92,2; 100,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>67,47; 88,34</t>
+          <t>63,69; 84,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>36,71; 69,6</t>
+          <t>25,14; 44,61</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>24,09; 36,56</t>
+          <t>24,33; 37,18</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>93,62; 98,85</t>
+          <t>93,31; 98,83</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>68,71; 84,03</t>
+          <t>70,36; 85,01</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>34,77; 56,57</t>
+          <t>33,22; 53,43</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>30,78%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>91,89%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>98,28%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>31,31%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>34,25%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>82,99%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>98,06%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>24,78%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>30,78%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>91,89%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>98,28%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>28,53%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>13,0; 62,73</t>
+          <t>12,08; 56,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>62,82; 95,32</t>
+          <t>78,38; 97,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>89,36; 100,0</t>
+          <t>90,2; 100,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15,48; 37,13</t>
+          <t>21,52; 46,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,1; 55,94</t>
+          <t>13,17; 62,12</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>79,12; 97,44</t>
+          <t>63,22; 95,78</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>91,19; 100,0</t>
+          <t>92,0; 100,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>21,97; 47,17</t>
+          <t>15,54; 37,85</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>16,31; 50,58</t>
+          <t>16,04; 51,55</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>76,91; 94,65</t>
+          <t>77,47; 95,05</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>92,73; 100,0</t>
+          <t>94,07; 100,0</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>21,28; 38,19</t>
+          <t>20,66; 36,21</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>28,22%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>80,23%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>77,43%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>39,77%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>21,63%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>72,05%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>62,04%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>32,19%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>28,22%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>80,23%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>77,43%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>34,84%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12,79; 32,02</t>
+          <t>19,14; 38,09</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>60,13; 82,53</t>
+          <t>68,4; 88,85</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>45,47; 75,5</t>
+          <t>61,85; 87,57</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>21,96; 42,61</t>
+          <t>29,96; 49,65</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>19,32; 39,11</t>
+          <t>12,79; 31,37</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>69,57; 88,28</t>
+          <t>60,05; 81,85</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>62,2; 87,88</t>
+          <t>46,02; 77,4</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>31,34; 51,03</t>
+          <t>20,77; 40,99</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>18,6; 32,6</t>
+          <t>18,64; 32,55</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>69,1; 83,2</t>
+          <t>68,34; 82,73</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>59,38; 80,0</t>
+          <t>59,72; 80,03</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>30,49; 44,8</t>
+          <t>27,47; 41,37</t>
         </is>
       </c>
     </row>
@@ -1489,62 +1489,62 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>30,04%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>77,05%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>61,66%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>7,35%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>24,36%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>75,36%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>61,42%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>7,83%</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>27,2%</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>76,22%</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>61,54%</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>7,57%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>30,04%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>77,05%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>61,66%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>7,38%</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>27,2%</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>76,22%</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>61,54%</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>17,27; 31,11</t>
+          <t>23,31; 37,58</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>68,51; 81,56</t>
+          <t>70,27; 82,3</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>53,87; 68,7</t>
+          <t>53,84; 69,03</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,95; 11,91</t>
+          <t>4,03; 12,26</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>23,72; 37,46</t>
+          <t>18,1; 31,32</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,03; 83,19</t>
+          <t>68,33; 81,11</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>54,26; 68,24</t>
+          <t>52,47; 68,32</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,1; 12,33</t>
+          <t>4,57; 12,45</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>23,02; 32,39</t>
+          <t>22,42; 32,2</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>71,45; 80,27</t>
+          <t>71,7; 80,6</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>55,98; 66,21</t>
+          <t>56,07; 66,7</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,11; 10,85</t>
+          <t>5,05; 10,9</t>
         </is>
       </c>
     </row>
@@ -1629,42 +1629,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>36,75%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>89,51%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>92,8%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>81,08%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>39,3%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>90,76%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>95,92%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>80,57%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>36,75%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>89,51%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>92,8%</t>
-        </is>
-      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>79,44%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>81,0%</t>
+          <t>80,31%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>31,2; 48,16</t>
+          <t>29,19; 44,71</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>85,75; 94,58</t>
+          <t>84,12; 93,42</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>92,13; 98,09</t>
+          <t>88,48; 95,89</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>73,94; 86,6</t>
+          <t>74,94; 86,3</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>29,17; 44,33</t>
+          <t>31,36; 47,75</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>83,71; 93,07</t>
+          <t>85,63; 94,61</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>88,28; 95,67</t>
+          <t>91,44; 98,17</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>74,9; 86,59</t>
+          <t>71,85; 85,19</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>32,68; 44,05</t>
+          <t>32,46; 43,73</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>86,41; 92,87</t>
+          <t>86,38; 93,23</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>91,75; 96,38</t>
+          <t>91,51; 96,32</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>76,59; 85,06</t>
+          <t>75,79; 84,76</t>
         </is>
       </c>
     </row>
@@ -1769,42 +1769,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>30,28%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>83,58%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>69,73%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>35,4%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>31,61%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>82,57%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>68,01%</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>30,85%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>30,28%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>83,58%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>69,73%</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>33,87%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>28,48; 34,87</t>
+          <t>27,03; 33,54</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>79,67; 85,52</t>
+          <t>81,08; 86,23</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>64,84; 71,83</t>
+          <t>66,34; 72,76</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>26,65; 34,43</t>
+          <t>31,94; 39,04</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>27,52; 34,08</t>
+          <t>28,18; 35,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>81,05; 86,03</t>
+          <t>79,61; 85,36</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>66,42; 72,96</t>
+          <t>64,57; 71,12</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>30,85; 38,18</t>
+          <t>29,0; 35,23</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>28,59; 33,27</t>
+          <t>28,41; 33,2</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>81,03; 84,86</t>
+          <t>81,2; 84,96</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>66,66; 71,2</t>
+          <t>66,74; 71,08</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>29,96; 35,62</t>
+          <t>31,41; 36,5</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,7 +1965,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -2073,42 +2073,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -2141,42 +2141,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>20969</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>32238</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>39915</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>6229</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>23050</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>23454</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>27915</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>14546</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>20969</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>32238</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>39915</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7372</t>
+          <t>7366</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>21918</t>
+          <t>13596</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>17104; 28231</t>
+          <t>15437; 27102</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>20165; 24842</t>
+          <t>28012; 35453</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>22963; 33397</t>
+          <t>34341; 44037</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6862; 28284</t>
+          <t>3134; 10654</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>15291; 26875</t>
+          <t>17905; 28400</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27814; 35639</t>
+          <t>20498; 24865</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34490; 44481</t>
+          <t>22449; 32616</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3848; 12313</t>
+          <t>4003; 12419</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>36211; 51951</t>
+          <t>35605; 51698</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>50890; 59722</t>
+          <t>50483; 59238</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>60226; 74554</t>
+          <t>60332; 74880</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13654; 40342</t>
+          <t>8477; 19357</t>
         </is>
       </c>
     </row>
@@ -2281,42 +2281,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>27</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2349,42 +2349,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>13630</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>46832</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>29112</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>23881</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>20906</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>40173</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>23275</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>17866</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>13630</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>46832</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>29112</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>27062</t>
+          <t>17491</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>44928</t>
+          <t>41371</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15219; 27306</t>
+          <t>9199; 19355</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>34208; 44980</t>
+          <t>41414; 51559</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17697; 30188</t>
+          <t>22571; 36837</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8794; 26491</t>
+          <t>16501; 32658</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9042; 19323</t>
+          <t>15074; 27533</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>40955; 51088</t>
+          <t>34649; 44884</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22021; 36119</t>
+          <t>17494; 30073</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18518; 37861</t>
+          <t>11593; 24707</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>27605; 42571</t>
+          <t>27563; 44605</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>79498; 93708</t>
+          <t>78315; 93894</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>43348; 62433</t>
+          <t>42567; 61579</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>29880; 59166</t>
+          <t>32404; 53982</t>
         </is>
       </c>
     </row>
@@ -2489,42 +2489,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>17</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2557,42 +2557,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>16856</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>44798</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>24331</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>9822</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>19103</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>41838</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>24526</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>9599</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>16856</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>44798</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>24331</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11359</t>
+          <t>9347</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>20958</t>
+          <t>19170</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>13294; 25574</t>
+          <t>11837; 23044</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>36100; 46298</t>
+          <t>38482; 49761</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18075; 31178</t>
+          <t>17979; 30549</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5965; 14583</t>
+          <t>5967; 14163</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>11831; 23051</t>
+          <t>13284; 25343</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>39168; 49823</t>
+          <t>36339; 46188</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18430; 31179</t>
+          <t>18902; 30905</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7320; 17145</t>
+          <t>5711; 14019</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>28506; 44758</t>
+          <t>28553; 45211</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>79190; 93729</t>
+          <t>79316; 93495</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>40743; 58059</t>
+          <t>40700; 58558</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14834; 27906</t>
+          <t>14236; 25759</t>
         </is>
       </c>
     </row>
@@ -2702,37 +2702,37 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>47</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>33</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2765,42 +2765,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>21551</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>53514</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>37347</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>36236</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>20293</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>48450</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>33770</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>23789</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>21551</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>53514</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>37347</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>39939</t>
+          <t>23900</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>63728</t>
+          <t>60136</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14673; 26708</t>
+          <t>15662; 28124</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>45822; 49680</t>
+          <t>50208; 54836</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>28296; 37935</t>
+          <t>32233; 41625</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16960; 31976</t>
+          <t>26395; 49664</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>15423; 28006</t>
+          <t>14778; 26880</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>50088; 54840</t>
+          <t>45805; 49680</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>31684; 41486</t>
+          <t>28731; 38187</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>28474; 53982</t>
+          <t>17810; 31605</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>33619; 51031</t>
+          <t>33957; 51893</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>98446; 103946</t>
+          <t>98121; 103923</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>63259; 77366</t>
+          <t>64785; 78270</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>51360; 83557</t>
+          <t>47304; 76077</t>
         </is>
       </c>
     </row>
@@ -2910,37 +2910,37 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>47</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2973,42 +2973,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>3508</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>22634</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>34906</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>12394</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>3267</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>14974</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>31747</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>8552</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>3508</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>22634</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>34906</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>13601</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>22153</t>
+          <t>21453</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1240; 5985</t>
+          <t>1377; 6450</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>11334; 17198</t>
+          <t>19305; 23988</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>28932; 32375</t>
+          <t>32034; 35516</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5342; 12814</t>
+          <t>8517; 18277</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1380; 6377</t>
+          <t>1257; 5927</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>19488; 23999</t>
+          <t>11407; 17281</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>32385; 35516</t>
+          <t>29786; 32375</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>8946; 19206</t>
+          <t>5532; 13477</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3415; 10592</t>
+          <t>3359; 10795</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>32820; 40390</t>
+          <t>33059; 40563</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>62953; 67890</t>
+          <t>63862; 67890</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>16008; 28728</t>
+          <t>15537; 27224</t>
         </is>
       </c>
     </row>
@@ -3113,42 +3113,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>28</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -3181,42 +3181,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>14749</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>39740</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>24279</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>19463</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>10092</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>32093</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>16462</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>14860</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>14749</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>39740</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>24279</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>23259</t>
+          <t>13529</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>38120</t>
+          <t>32992</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5968; 14939</t>
+          <t>10007; 19913</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>26785; 36760</t>
+          <t>33881; 44010</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12066; 20036</t>
+          <t>19395; 27460</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10136; 19673</t>
+          <t>14662; 24302</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>10101; 20444</t>
+          <t>5968; 14637</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>34462; 43726</t>
+          <t>26746; 36455</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19504; 27557</t>
+          <t>12213; 20539</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>17611; 28671</t>
+          <t>9505; 18759</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>18402; 32249</t>
+          <t>18442; 32204</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>65005; 78271</t>
+          <t>64288; 77824</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>34376; 46312</t>
+          <t>34574; 46332</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>31213; 45854</t>
+          <t>26019; 39179</t>
         </is>
       </c>
     </row>
@@ -3321,37 +3321,37 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>122</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>105</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -3389,42 +3389,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>33284</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>93824</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>72582</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>10392</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>26951</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>87954</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>68882</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>9421</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>33284</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>93824</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>72582</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>11507</t>
+          <t>9593</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>20928</t>
+          <t>19985</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>19108; 34423</t>
+          <t>25826; 41633</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>79954; 95179</t>
+          <t>85575; 100218</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>60412; 77042</t>
+          <t>63378; 81263</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4921; 14834</t>
+          <t>5693; 17329</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>26276; 41506</t>
+          <t>20023; 34659</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>86500; 101308</t>
+          <t>79749; 94662</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>63879; 80337</t>
+          <t>58846; 76621</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>6392; 19235</t>
+          <t>5599; 15260</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>50972; 71727</t>
+          <t>49654; 71291</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>170400; 191439</t>
+          <t>171001; 192218</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>128681; 152188</t>
+          <t>128896; 153331</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>14347; 30428</t>
+          <t>13338; 28775</t>
         </is>
       </c>
     </row>
@@ -3529,42 +3529,42 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>157</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>198</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>158</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -3597,42 +3597,42 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>35492</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>116219</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>129200</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>128837</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>35433</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>104869</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>124370</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>106050</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>35492</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>116219</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>129200</t>
-        </is>
-      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>127034</t>
+          <t>111608</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>233085</t>
+          <t>240446</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>28134; 43426</t>
+          <t>28195; 43183</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>99072; 109273</t>
+          <t>109217; 121300</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>119453; 127179</t>
+          <t>123178; 133505</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>97323; 113982</t>
+          <t>119083; 137137</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>28170; 42811</t>
+          <t>28278; 43054</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>108692; 120835</t>
+          <t>98938; 109308</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>122903; 133196</t>
+          <t>118557; 127282</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>116941; 135201</t>
+          <t>100953; 119695</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>61024; 82255</t>
+          <t>60612; 81668</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>212024; 227889</t>
+          <t>211964; 228753</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>246704; 259139</t>
+          <t>246045; 258988</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>220382; 244777</t>
+          <t>226922; 253777</t>
         </is>
       </c>
     </row>
@@ -3737,42 +3737,42 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>639</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>571</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>352</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>239</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>569</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>535</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>305</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>639</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>571</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>352</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3805,42 +3805,42 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>160038</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>449801</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>391673</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>247254</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
           <t>159096</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>393806</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>350945</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>204684</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>160038</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>449801</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>391673</t>
-        </is>
-      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>261135</t>
+          <t>201895</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>465819</t>
+          <t>449149</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>143346; 175521</t>
+          <t>142875; 177263</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>380002; 407906</t>
+          <t>436342; 464031</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>334612; 370677</t>
+          <t>372627; 408700</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>176846; 228486</t>
+          <t>223101; 272696</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>145465; 180130</t>
+          <t>141828; 176193</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>436171; 462974</t>
+          <t>379722; 407139</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>373103; 409824</t>
+          <t>333199; 367020</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>234238; 289888</t>
+          <t>181945; 221074</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>295036; 343331</t>
+          <t>293215; 342599</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>822566; 861399</t>
+          <t>824311; 862397</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>718387; 767403</t>
+          <t>719347; 766056</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>426337; 506888</t>
+          <t>416526; 483894</t>
         </is>
       </c>
     </row>
